--- a/inst/extdata/projects/Example/ProjectConfiguration.xlsx
+++ b/inst/extdata/projects/Example/ProjectConfiguration.xlsx
@@ -382,11 +382,6 @@
           <t>Models/Simulations/</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Path to the folder with pkml simulation files; relative to the location of this file</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -399,11 +394,6 @@
           <t>Configurations/</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Path to the folder with excel files with parametrization; relative to the location of this file</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -416,11 +406,6 @@
           <t>ModelParameters.xlsx</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Name of the excel file with global model parametrization. Must be located in the "paramsFolder"</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -433,11 +418,6 @@
           <t>Individuals.xlsx</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Name of the excel file with individual-specific model parametrization. Must be located in the "paramsFolder"</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -450,11 +430,6 @@
           <t>Populations.xlsx</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Name of the excel file with population information. Must be located in the "paramsFolder"</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -467,11 +442,6 @@
           <t>PopulationsCSV</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Name of the folder containing population defined in files</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -484,11 +454,6 @@
           <t>Scenarios.xlsx</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Name of the excel file with scenario definitions. Must be located in the "paramsFolder"</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -501,11 +466,6 @@
           <t>Applications.xlsx</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Name of the excel file scenario-specific parameters such as application protocol parameters. Must be located in the "paramsFolder"</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -518,11 +478,6 @@
           <t>Plots.xlsx</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Name of the excel file with plot definitions. Must be located in the "paramsFolder"</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -535,11 +490,6 @@
           <t>Data/</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Path to the folder where experimental data files are located; relative to the location of this file</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -549,12 +499,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>TestProject_TimeValuesData.xlsx</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Name of the excel file with experimental data. Must be located in the "dataFolder"</t>
+          <t>Aciclovir_TimeValuesData.xlsx</t>
         </is>
       </c>
     </row>
@@ -569,11 +514,6 @@
           <t>esqlabs_dataImporter_configuration.xml</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Name of data importer configuration file in xml format used to load the data. Must be located in the "dataFolder"</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -584,11 +524,6 @@
       <c r="B14" t="inlineStr">
         <is>
           <t>Results/</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Path to the folder where the results should be saved to; relative to the location of this file</t>
         </is>
       </c>
     </row>
